--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-009_承認待ち一覧_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-009_承認待ち一覧_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="10496550"/>
+    <ext cx="8572500" cy="10706100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-009 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-009 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1966,7 +1966,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：@EnableMethodSecurity・handleAccessDenied・handleTypeMismatch の定義元を ONL-001 に統一、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：@EnableMethodSecurity・handleAccessDenied・handleTypeMismatch の定義元を ONL-001 に統一、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3709,7 +3710,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Long.valueOf(jwt.getSubject())</t>
+          <t>Long.valueOf(auth.getName())</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -3951,7 +3952,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public PendingApprovalListResponse pending(@RequestParam(name = "requestType", required = false) String requestType, @RequestParam(name = "stepNo", required = false) Integer stepNo, @AuthenticationPrincipal Jwt jwt)</t>
+          <t>public PendingApprovalListResponse pending(@RequestParam(name = "requestType", required = false) String requestType, @RequestParam(name = "stepNo", required = false) Integer stepNo, Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4055,17 +4056,17 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub＝users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -4116,7 +4117,7 @@
         <is>
           <t>1. Spring Security が Bearer トークンを検証する（無効・期限切れ → AuthenticationEntryPoint が 401 / E-001 の JSON）
 2. @PreAuthorize でロール（ROLE_MANAGER / ROLE_ADMIN）を確認する
-3. userId = Long.valueOf(jwt.getSubject());
+3. userId = Long.valueOf(auth.getName());
 4. return approvalService.listPending(userId, requestType, stepNo);</t>
         </is>
       </c>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-009_承認待ち一覧_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-009_承認待ち一覧_オンライン詳細設計書.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-009 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-009 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -853,7 +853,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>requestType が LEAVE/CLOCK_CORRECTION 以外／stepNo が 1,2 以外・整数でない</t>
+          <t>requestType が LEAVE/CLOCK_CORRECTION/BREAK_CORRECTION 以外／stepNo が 1,2 以外・整数でない</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E33"/>
+  <dimension ref="A2:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1484,112 +1484,120 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>requestType＝BREAK_CORRECTION</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>types＝[BREAK_CORRECTION] で findPending が呼ばれる</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>E-002 にならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>requestType 省略</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>types＝[LEAVE, CLOCK_CORRECTION, BREAK_CORRECTION] の順で呼ばれる</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>requestType＝"break_correction"（小文字）</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>E-002 / 400</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>大文字小文字を区別する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>9.2 ApprovalStepRepository#findPending（@DataJpaTest）</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>自分宛の1段目 WAITING で request が PENDING・current_step＝1</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>1件含まれる</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>他人宛の1段目 WAITING</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>含まれない</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>step.status が APPROVED / RETURNED / REJECTED</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>含まれない</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1599,24 +1607,20 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>request.status が WITHDRAWN / RETURNED / REJECTED（2段目 WAITING が残る）</t>
+          <t>自分宛の1段目 WAITING で request が PENDING・current_step＝1</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>含まれない</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>取下げ・差戻し後の残骸ステップ</t>
-        </is>
-      </c>
+          <t>1件含まれる</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -1631,7 +1635,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>2段目 WAITING だが request.current_step＝1</t>
+          <t>他人宛の1段目 WAITING</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1639,11 +1643,7 @@
           <t>含まれない</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>1段目が未処理</t>
-        </is>
-      </c>
+      <c r="E22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1653,26 +1653,22 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>ADMIN(admin＝true)：current_step＝2 の2段目</t>
+          <t>step.status が APPROVED / RETURNED / REJECTED</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>含まれ、step1ApprovedAt に1段目の acted_at が入る</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>approver_id は NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
+          <t>含まれない</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>18</t>
@@ -1685,7 +1681,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>admin＝false で2段目</t>
+          <t>request.status が WITHDRAWN / RETURNED / REJECTED（2段目 WAITING が残る）</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1693,9 +1689,13 @@
           <t>含まれない</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="34" customHeight="1">
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>取下げ・差戻し後の残骸ステップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>19</t>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>申請者が自分自身（ADMIN の自分の申請の2段目）</t>
+          <t>2段目 WAITING だが request.current_step＝1</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1716,7 +1716,11 @@
           <t>含まれない</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>1段目が未処理</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -1731,58 +1735,93 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
+          <t>ADMIN(admin＝true)：current_step＝2 の2段目</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>含まれ、step1ApprovedAt に1段目の acted_at が入る</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>approver_id は NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>admin＝false で2段目</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>含まれない</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>申請者が自分自身（ADMIN の自分の申請の2段目）</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>含まれない</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
           <t>並び順</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>submitted_at 昇順、同一なら step.id 昇順</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>9.3 ApprovalController（MockMvc / API テスト）</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="E29" s="7" t="inlineStr"/>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1792,90 +1831,205 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
+          <t>request_type＝BREAK_CORRECTION・自分宛の1段目 WAITING・PENDING</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1件含まれる。days は null</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>types に含めたときのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>types＝[LEAVE, CLOCK_CORRECTION] で BREAK_CORRECTION の申請</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>含まれない</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>IN による絞込</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>9.3 ApprovalController（MockMvc / API テスト）</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
           <t>MANAGER のトークンで呼出し</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>200、items の各項目が「4. 入出力」どおり</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>EMPLOYEE のトークン</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>403 E-010</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>トークンなし</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>requestType＝xxx／stepNo＝abc</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>400 E-002「入力内容が正しくありません。」</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr"/>
+      <c r="E38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>requestType＝BREAK_CORRECTION で MANAGER が呼出し</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>200。items[].requestType は全て BREAK_CORRECTION</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1888,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1971,6 +2125,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="64" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請（BREAK_CORRECTION）に対応：requestType の許容値と省略時の対象に BREAK_CORRECTION を追加（それ以外は E-002）。listPending の種別定数を RequestType 参照に修正。mapping に corrected_break_* を追記。テスト観点を追加</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3038,12 +3215,12 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>LEAVE または CLOCK_CORRECTION</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION のいずれか</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>上記以外 → E-002「入力内容が正しくありません。」（HTTP 400）。省略時は両方を返す（SCR-201 の「すべて」）</t>
+          <t>上記以外 → E-002「入力内容が正しくありません。」（HTTP 400）。省略時は 3 種別すべてを返す（SCR-201 の「すべて」）</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3407,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION</t>
         </is>
       </c>
       <c r="E16" s="9" t="n"/>
@@ -3350,7 +3527,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>yyyy-MM-dd（打刻修正は通常 startDate と同じ）</t>
+          <t>yyyy-MM-dd（打刻修正・休憩離席修正は startDate と同じ）</t>
         </is>
       </c>
       <c r="E21" s="9" t="n"/>
@@ -3374,7 +3551,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>requests.days（例 3.0、半日 0.5）。打刻修正は null</t>
+          <t>requests.days（例 3.0、半日 0.5）。打刻修正・休憩離席修正は null</t>
         </is>
       </c>
       <c r="E22" s="9" t="n"/>
@@ -3760,7 +3937,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>requestType∈{LEAVE,CLOCK_CORRECTION}、stepNo∈{1,2}（いずれも省略可）</t>
+          <t>requestType∈{LEAVE,CLOCK_CORRECTION,BREAK_CORRECTION}、stepNo∈{1,2}（いずれも省略可）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3905,7 +4082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F89"/>
+  <dimension ref="A2:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3914,6 +4091,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4289,7 +4467,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION / null</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION / null</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -4348,7 +4526,7 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
-    <row r="28" ht="244" customHeight="1">
+    <row r="28" ht="259" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -4357,7 +4535,7 @@
       <c r="B28" s="12" t="inlineStr">
         <is>
           <t>User actor = requireApprover(userId);                                  // ③ E-010（ONL-010 の共通メソッド）
-if (requestType != null &amp;&amp; !List.of("LEAVE", "CLOCK_CORRECTION").contains(requestType))
+if (requestType != null &amp;&amp; !List.of(RequestType.LEAVE, RequestType.CLOCK_CORRECTION, RequestType.BREAK_CORRECTION).contains(requestType))
     throw invalidInput();                                              // ④ E-002 / 400
 if (stepNo != null &amp;&amp; stepNo != 1 &amp;&amp; stepNo != 2)
     throw invalidInput();
@@ -4367,7 +4545,7 @@
         : (allowed.contains(stepNo) ? List.of(stepNo) : List.of());
 if (stepNos.isEmpty()) return new PendingApprovalListResponse(List.of());
 List&lt;String&gt; types = (requestType == null)
-        ? List.of("LEAVE", "CLOCK_CORRECTION") : List.of(requestType);
+        ? List.of(RequestType.LEAVE, RequestType.CLOCK_CORRECTION, RequestType.BREAK_CORRECTION) : List.of(requestType);
 List&lt;PendingApprovalRow&gt; rows =
         approvalStepRepository.findPending(userId, admin, types, stepNos);   // ⑥
 return new PendingApprovalListResponse(
@@ -5265,7 +5443,8 @@
       </c>
       <c r="D83" s="9" t="n"/>
       <c r="E83" s="9" t="n"/>
-      <c r="F83" s="10" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="10" t="n"/>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
@@ -5285,7 +5464,8 @@
       </c>
       <c r="D84" s="9" t="n"/>
       <c r="E84" s="9" t="n"/>
-      <c r="F84" s="10" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="10" t="n"/>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -5305,7 +5485,8 @@
       </c>
       <c r="D85" s="9" t="n"/>
       <c r="E85" s="9" t="n"/>
-      <c r="F85" s="10" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="10" t="n"/>
     </row>
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -5325,7 +5506,8 @@
       </c>
       <c r="D86" s="9" t="n"/>
       <c r="E86" s="9" t="n"/>
-      <c r="F86" s="10" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="10" t="n"/>
     </row>
     <row r="87" ht="19" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -5345,7 +5527,8 @@
       </c>
       <c r="D87" s="9" t="n"/>
       <c r="E87" s="9" t="n"/>
-      <c r="F87" s="10" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="10" t="n"/>
     </row>
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
@@ -5365,7 +5548,8 @@
       </c>
       <c r="D88" s="9" t="n"/>
       <c r="E88" s="9" t="n"/>
-      <c r="F88" s="10" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="10" t="n"/>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -5385,25 +5569,45 @@
       </c>
       <c r="D89" s="9" t="n"/>
       <c r="E89" s="9" t="n"/>
-      <c r="F89" s="10" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="10" t="n"/>
+    </row>
+    <row r="90" ht="49" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>申請種別 BREAK_CORRECTION</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>種別絞込（requestType）と省略時の対象に BREAK_CORRECTION を含める。休憩・離席修正申請の行は days＝null、startDate＝endDate（対象日）。休憩の種別・時刻は一覧に出さず、承認画面で ONL-007 を呼んで確認する。1段目・2段目の対象判定、自分の申請の除外は他種別と同じ</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="79">
     <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C83:G83"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="C87:F87"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C89:F89"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="C88:F88"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="C54:F54"/>
     <mergeCell ref="C10:F10"/>
@@ -5415,30 +5619,33 @@
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="C86:G86"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C84:G84"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A61:F61"/>
+    <mergeCell ref="C87:G87"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="B59:F59"/>
+    <mergeCell ref="C89:G89"/>
     <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C88:G88"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="C53:F53"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="C86:F86"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="C84:F84"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A45:F45"/>
@@ -5453,10 +5660,10 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="C90:G90"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C85:F85"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="C9:F9"/>
@@ -5479,7 +5686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F59"/>
+  <dimension ref="A2:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5942,7 +6149,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
+    <row r="18" ht="49" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>request_type</t>
@@ -5970,7 +6177,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION（ck_req_type、V5 で BREAK_CORRECTION を追加）。絞込は IN :types</t>
         </is>
       </c>
     </row>
@@ -6190,443 +6397,443 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
+          <t>corrected_break_kind / start / end</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>correctedBreakKind / Start / End</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>String / LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION のみ（V5）。一覧では出力しない。内容は ONL-007 の詳細取得で確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>○ 検索条件（PENDING）</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>○ 検索条件（PENDING）</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>current_step</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>currentStep</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>○ 検索条件（＝step_no）</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>現在の承認段（1/2）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>submitted_at</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>submittedAt</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>○ 出力・並び順</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>提出日時（JST）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_requests_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>■ users</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>○ 出力(applicantId)・結合・実行者の取得</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
           <t>password_hash</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>passwordHash</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>BCrypt ハッシュ。VARCHAR(255)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>○ 出力(applicantName)</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>○ 実行者の権限確認</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>EMPLOYEE / MANAGER / ADMIN</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>departmentId</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>○ 結合</t>
+          <t>○ 実行者の権限確認</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>FK departments</t>
+          <t>EMPLOYEE / MANAGER / ADMIN</t>
         </is>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>manager_id</t>
+          <t>department_id</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>managerId</t>
+          <t>departmentId</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -6641,34 +6848,34 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>○ 結合</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>FK users</t>
+          <t>FK departments</t>
         </is>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>hire_date</t>
+          <t>manager_id</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>hireDate</t>
+          <t>managerId</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -6676,311 +6883,343 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>FK users</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
+          <t>hire_date</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>hireDate</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>○ 実行者の有効確認</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>ACTIVE / INACTIVE（既定 ACTIVE）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>■ departments</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="10" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>○ 結合</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>○ 出力(departmentName)</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力(departmentName)</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_departments_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n"/>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="10" t="n"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>実行者の取得（UserRepository#findById）</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
-        </is>
-      </c>
+      <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="n"/>
       <c r="D53" s="9" t="n"/>
       <c r="E53" s="9" t="n"/>
       <c r="F53" s="10" t="n"/>
     </row>
-    <row r="54" ht="184" customHeight="1">
+    <row r="54" ht="34" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
+          <t>実行者の取得（UserRepository#findById）</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n"/>
+    </row>
+    <row r="55" ht="184" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
           <t>承認待ちステップ検索（ApprovalStepRepository#findPending）</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>SELECT s.id, s.step_no, r.id, r.request_type, u.id, u.name, d.name,
        r.start_date, r.end_date, r.days, r.submitted_at, s1.acted_at
@@ -6996,67 +7235,43 @@
  ORDER BY r.submitted_at ASC, s.id ASC</t>
         </is>
       </c>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="10" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>7.3 設定値</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="10" t="n"/>
-    </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="n"/>
-    </row>
-    <row r="58" ht="49" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>（Bean）Clock / AppTime</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>config/ClockConfig.java・AppTime.java</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>日時の ISO 8601（+09:00）変換は AppTime.toIso を使う</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>ONL-002 で定義済み。新規設定なし</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -7064,44 +7279,68 @@
     <row r="59" ht="49" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
+          <t>（Bean）Clock / AppTime</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>application.properties</t>
+          <t>config/ClockConfig.java・AppTime.java</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Asia/Tokyo。LocalDateTime の DB 読み書きを JST に固定</t>
+          <t>日時の ISO 8601（+09:00）変換は AppTime.toIso を使う</t>
         </is>
       </c>
       <c r="D59" s="10" t="n"/>
       <c r="E59" s="7" t="inlineStr">
         <is>
+          <t>ONL-002 で定義済み。新規設定なし</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="49" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>application.properties</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Asia/Tokyo。LocalDateTime の DB 読み書きを JST に固定</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
           <t>ONL-002 で定義済み</t>
         </is>
       </c>
-      <c r="F59" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B53:F53"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C60:D60"/>
     <mergeCell ref="C58:D58"/>
-    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E60:F60"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
